--- a/docs/sprint2/audit/audit-Haievskyi.xlsx
+++ b/docs/sprint2/audit/audit-Haievskyi.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -27,26 +27,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Arial"/>
       <b val="1"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <sz val="10"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D9EAD3"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -59,16 +48,16 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00999999"/>
+        <color rgb="00000000"/>
       </left>
       <right style="thin">
-        <color rgb="00999999"/>
+        <color rgb="00000000"/>
       </right>
       <top style="thin">
-        <color rgb="00999999"/>
+        <color rgb="00000000"/>
       </top>
       <bottom style="thin">
-        <color rgb="00999999"/>
+        <color rgb="00000000"/>
       </bottom>
     </border>
   </borders>
@@ -77,10 +66,10 @@
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -448,16 +437,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
     <col width="8" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="55" customWidth="1" min="5" max="5"/>
-    <col width="55" customWidth="1" min="6" max="6"/>
-    <col width="26" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
+    <col width="50" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -478,20 +468,25 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Критерій</t>
+          <t>Критерій (моя оцінка)</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Опис дефекту (пункт чек-листа, цитата)</t>
+          <t>Пункт чек-листа</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Пропозиція виправлення</t>
+          <t>Що знайдено (запис під час перевірки)</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Пропозиція (чернетка)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Результат зведення</t>
         </is>
@@ -520,15 +515,20 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>п. 1, 4, 5: «обов'язковість полів позначено у формі зірочкою» — які поля обов'язкові, не визначено; не описано реакцію на вже зареєстровану адресу email і на пароль, що не відповідає правилам.</t>
+          <t>п. 1, 5</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>«…Обов'язкові всі поля, крім «номер будинку» (потребує підтвердження замовником). Якщо адреса email уже зареєстрована, система показує «A customer with this email address already exists.», обліковий запис не створюється; якщо пароль не відповідає правилам — повідомлення за GUI-50, обліковий запис не створюється».</t>
+          <t>Зірочка — це про вигляд форми, а не перелік. Які поля обов'язкові — з вимоги не зрозуміло. Реакції на email, який уже зареєстрований, немає.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Список обов'язкових полів у тексті + повідомлення для вже зареєстрованого email.</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>Прийнято, № 5 реєстру</t>
         </is>
@@ -542,7 +542,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>F-100</t>
+          <t>F-20</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -552,22 +552,27 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Простежуваність</t>
+          <t>Однозначність</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>п. 2: «Обмеження на кількість одиниць у рядку визначає вимога BL-25» — вимоги BL-25 у специфікації немає, зв'язок не простежується.</t>
+          <t>п. 4</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>«…Кількість одиниць у рядку — від 1 до 99 включно (BL-10, BL-20, BL-40)».</t>
+          <t>«на відповідну сторінку». У demo після входу відкривається кабінет, а якщо входити з кошика — оформлення. У вимозі немає ні того, ні іншого.</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>Прийнято, № 17 реєстру</t>
+          <t>Розписати обидва випадки: звичайний вхід → кабінет; вхід на кроці «Sign in» → наступний крок оформлення.</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>Прийнято, № 1 реєстру</t>
         </is>
       </c>
     </row>
@@ -579,7 +584,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>F-110</t>
+          <t>F-30</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -589,22 +594,27 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Однозначність</t>
+          <t>Здійсненність</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>п. 5: крок «Billing Address» (платіжна адреса) описано як «підтверджує адресу доставки»; термін «адреса доставки» у 1.3 відсутній, billing і shipping address — різні поняття.</t>
+          <t>єдиний пункт</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Термін «Адреса доставки» додано до 1.3: «адреса, за якою доставляється замовлення; у версії 1.0 вводиться на кроці «Billing Address» і збігається з платіжною адресою». У F-110: «на кроці 3 «Billing Address» підтверджує адресу доставки (див. 1.3)…».</t>
+          <t>1 секунда «незалежно від поштового провайдера» — це не залежить від нашої системи.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Прийнято, № 4 реєстру</t>
+          <t>Обмежитись часом, за який система відправляє лист, і строком дії посилання.</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Прийнято, № 18 реєстру</t>
         </is>
       </c>
     </row>
@@ -616,7 +626,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>F-120</t>
+          <t>F-50</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -626,22 +636,27 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Несуперечливість</t>
+          <t>Повнота</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>п. 2: F-120 «додати товар до списку обраного … без входу в систему» суперечить GUI-40 (гостю — «Unauthorized…», товар не додається) і ролям 2.1 (обране — лише зареєстрованому покупцю).</t>
+          <t>п. 1</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>F-120: «Зареєстрований покупець, який увійшов у систему, додає товар до списку обраного кнопкою «Add to favourites»; для гостя поведінку визначає GUI-40. Список обраного доступний у кабінеті («My favorites»), де позицію можна видалити».</t>
+          <t>Повзунок ціни 1–200, а інструменти в гривнях коштують і тисячі — дорожчі за 200 товари фільтром не знайти.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Прийнято, № 11 реєстру</t>
+          <t>Межі повзунка — від мінімальної до максимальної ціни в каталозі.</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>Відхилено на обговоренні (див. «Спірні»)</t>
         </is>
       </c>
     </row>
@@ -653,7 +668,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>F-20</t>
+          <t>F-90</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -668,17 +683,22 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>п. 1, 4 чек-листа: «Після успішного входу система перенаправляє користувача на відповідну сторінку» — «відповідна» не визначена; тест-кейс входу не має одного очікуваного результату.</t>
+          <t>п. 4</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>«Після успішного входу система перенаправляє користувача на сторінку особистого кабінету «My account» (/account); якщо вхід виконано на кроці «Sign in» оформлення замовлення — на крок «Billing Address»».</t>
+          <t>«миттєво» і «без помилок» кожен розуміє по-своєму.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Прийнято, № 1 реєстру</t>
+          <t>Показувати «Product added to shopping cart.» і оновлювати лічильник кошика, не довше 2 с.</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>Прийнято, № 22 реєстру; при зведенні перекласифіковано в тестопридатність (див. «Спірні»)</t>
         </is>
       </c>
     </row>
@@ -690,7 +710,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>F-30</t>
+          <t>F-100</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -700,22 +720,27 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Здійсненність</t>
+          <t>Простежуваність</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>«гарантує його доставку до поштової скриньки … не довше ніж за 1 секунду незалежно від поштового провайдера» — доставка залежить від сторонніх поштових серверів, які продукт не контролює.</t>
+          <t>п. 2</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>«…система передає лист із посиланням поштовому сервісу не пізніше ніж за 30 с після надсилання форми і показує повідомлення про надсилання; посилання дійсне 24 год» (значення потребують підтвердження замовником).</t>
+          <t>Посилання на BL-25 — такої вимоги в SRS немає.</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>Прийнято, № 18 реєстру</t>
+          <t>Послатися на BL-10 / BL-20, де є межі кількості.</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>Прийнято, № 17 реєстру</t>
         </is>
       </c>
     </row>
@@ -727,7 +752,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>F-50</t>
+          <t>F-110</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -737,22 +762,27 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Повнота</t>
+          <t>Однозначність</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Повзунок ціни «від 1 до 200» не відповідає реальним цінам інструментів у гривнях.</t>
+          <t>п. 5</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Діапазон повзунка від мінімальної до максимальної ціни каталогу.</t>
+          <t>Крок «Billing Address» — це платіжна адреса, а у вимозі «адреса доставки». Для e-commerce це різні речі.</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>Відхилено на обговоренні (див. «Спірні»)</t>
+          <t>Визначити в 1.3, що в цій версії це одна адреса.</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>Прийнято, № 4 реєстру</t>
         </is>
       </c>
     </row>
@@ -764,7 +794,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>F-90</t>
+          <t>F-120</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -774,22 +804,27 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Тестопридатність</t>
+          <t>Несуперечливість</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>«додає товар у кошик … миттєво і без помилок» — «миттєво», «без помилок» не дають критерію «пройдено / не пройдено».</t>
+          <t>п. 2</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>«Натискання «Add to cart» додає товар у кошик у кількості з поля «Quantity»; не пізніше ніж за 2 с з'являється повідомлення «Product added to shopping cart.», а лічильник кошика в шапці збільшується на цю кількість…».</t>
+          <t>«без входу в систему» — а GUI-40: гостю показується «Unauthorized…», і товар НЕ додається.</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>Прийнято, № 22 реєстру</t>
+          <t>F-120 — тільки для покупця, що увійшов; для гостя — посилання на GUI-40.</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>Прийнято, № 11 реєстру</t>
         </is>
       </c>
     </row>
@@ -801,7 +836,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>GUI-100</t>
+          <t>GUI-30</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -811,22 +846,27 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Тестопридатність</t>
+          <t>Несуперечливість</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>«Кольорова схема … приємною і сучасною, а шрифти — легкими для читання» — суб'єктивні оцінки, спостережуваного критерію немає.</t>
+          <t>п. 2</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>«Основний текст на всіх сторінках — шрифтом не менше 14 px; контраст тексту до фону — не менше 4,5:1 (WCAG 2.1, рівень AA); перевірка — Lighthouse або axe DevTools».</t>
+          <t>Quantity приймає 0…100, а кошик (BL-10) — 1…99. Через UI можна ввести 0 або 100, які модуль відхилить.</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>Прийнято, № 23 реєстру</t>
+          <t>GUI-30: 1…99, «−» неактивна на 1, «+» — на 99.</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>Прийнято, № 12 реєстру</t>
         </is>
       </c>
     </row>
@@ -838,7 +878,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>GUI-30</t>
+          <t>GUI-40</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -853,17 +893,22 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>п. 2: GUI-30 «приймає значення від 0 до 100» суперечить BL-10 / BL-40 (qty від 1 до 99): інтерфейс дозволяє кількість, яку модуль відхиляє.</t>
+          <t>п. 2</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>GUI-30: «…приймає цілі значення від 1 до 99; значення за замовчуванням — 1; на межах кнопка «−» (при 1) або «+» (при 99) неактивна; введене вручну значення поза межами замінюється найближчою межею».</t>
+          <t>Те саме, що Г-08, тільки з боку GUI: кнопка для гостя дає «Unauthorized», а F-120 дозволяє.</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>Прийнято, № 12 реєстру</t>
+          <t>Див. Г-08.</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>Об'єднано з Г-08 при зведенні → № 11 реєстру</t>
         </is>
       </c>
     </row>
@@ -890,15 +935,20 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>п. 4: «відображається біля відповідного поля або у верхній частині форми» — два допустимі місця, тест має два очікувані результати.</t>
+          <t>п. 4</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>«Повідомлення про помилку валідації відображається текстом безпосередньо під відповідним полем; форма з помилками не надсилається, введені дані у полях зберігаються».</t>
+          <t>«біля відповідного поля або у верхній частині форми» — два варіанти, тест не знає, що чекати.</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>Лише під полем.</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>Прийнято, № 3 реєстру</t>
         </is>
@@ -912,7 +962,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>GUI-60 (форма реєстрації)</t>
+          <t>GUI-60 (×2)</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -927,15 +977,20 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>п. 1, 2: ідентифікатор GUI-60 присвоєно двом різним вимогам — формі входу і формі реєстрації; посилання «GUI-60» неоднозначне.</t>
+          <t>п. 2</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>Форма входу лишається GUI-60; формі реєстрації присвоєно вільний проміжний ID GUI-65.</t>
+          <t>GUI-60 стоїть двічі — форма входу і форма реєстрації.</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>Реєстрації дати новий ID, наприклад GUI-65.</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>Прийнято, № 14 реєстру</t>
         </is>
@@ -964,17 +1019,64 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>«не менше 8K (7680×4320) без стиснення … не довше ніж за 50 мс кожне за будь-якого з'єднання» — нестиснене 8K-зображення ≈ 100 МБ, за 50 мс фізично недосяжно навіть на гігабітному каналі.</t>
+          <t>єдиний пункт</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>«Зображення на картках каталогу — не менше 400×400 пікселів, на сторінці товару — не менше 1000×1000 пікселів, формат JPEG або WebP; за з'єднання 10 Мбіт/с зображення сторінки товару завантажується не довше ніж за 1 с» (потребує підтвердження замовником).</t>
+          <t>8K без стиснення ≈ 100 МБ на одне зображення, і завантаження за 50 мс за будь-якого з'єднання. Фізично неможливо.</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Прийнято, № 19 реєстру</t>
+          <t>Зменшити вимоги до зображень.</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>Прийнято, № 19 реєстру; виправлення доопрацьовано при зведенні (400×400 / 1000×1000, ≤ 1 с при 10 Мбіт/с)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Г-14</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>GUI-100</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Тестопридатність</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>практичний тест</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>«приємною і сучасною», «легкими для читання» — суб'єктивно, нема що виміряти.</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>Мінімальний розмір шрифту і контраст за WCAG AA, перевірка Lighthouse.</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>Прийнято, № 23 реєстру</t>
         </is>
       </c>
     </row>
@@ -989,11 +1091,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="70" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1059,17 +1161,17 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Знайдено (всього)</t>
+          <t>Записів в аркуші</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Прийнято до реєстру</t>
+          <t>Прийнято до реєстру як окремий дефект</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
@@ -1079,7 +1181,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Відхилено</t>
+          <t>Об'єднано з іншим записом при зведенні</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -1089,47 +1191,45 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>— Однозначність</t>
+          <t>Відхилено на обговоренні</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>— Повнота</t>
+          <t>Перекласифіковано при зведенні</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>— Несуперечливість</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="n">
-        <v>2</v>
-      </c>
+          <t>Записи за критерієм (моя оцінка)</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>— Простежуваність</t>
+          <t>— Однозначність</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>— Здійсненність</t>
+          <t>— Повнота</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
@@ -1139,11 +1239,53 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
+          <t>— Несуперечливість</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>— Простежуваність</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>— Здійсненність</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
           <t>— Тестопридатність</t>
         </is>
       </c>
-      <c r="B14" s="2" t="n">
-        <v>2</v>
+      <c r="B17" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Примітка</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Колонки «Що знайдено» і «Пропозиція» — формулювання до зведення; узгоджений текст дефекту і виправлення — у requirements-defects.xlsx, аркуш «Реєстр».</t>
+        </is>
       </c>
     </row>
   </sheetData>
